--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25074,6 +25074,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1075">
+      <c r="A1075" s="1" t="n">
+        <v>46279.2916666667</v>
+      </c>
+      <c r="B1075" t="n">
+        <v>9345</v>
+      </c>
+      <c r="C1075" t="n">
+        <v>11.2200002670288</v>
+      </c>
+      <c r="D1075" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="E1075" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="F1075" t="n">
+        <v>11.1400003433228</v>
+      </c>
+      <c r="G1075" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25097,6 +25097,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1076">
+      <c r="A1076" s="1" t="n">
+        <v>46280.2916666667</v>
+      </c>
+      <c r="B1076" t="n">
+        <v>9676</v>
+      </c>
+      <c r="C1076" t="n">
+        <v>11.1800003051758</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="E1076" t="n">
+        <v>11.1400003433228</v>
+      </c>
+      <c r="F1076" t="n">
+        <v>11.1599998474121</v>
+      </c>
+      <c r="G1076" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25120,6 +25120,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1077">
+      <c r="A1077" s="1" t="n">
+        <v>46281.2916666667</v>
+      </c>
+      <c r="B1077" t="n">
+        <v>21841</v>
+      </c>
+      <c r="C1077" t="n">
+        <v>11.6199998855591</v>
+      </c>
+      <c r="D1077" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E1077" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="F1077" t="n">
+        <v>11.5799999237061</v>
+      </c>
+      <c r="G1077" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25143,6 +25143,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1078">
+      <c r="A1078" s="1" t="n">
+        <v>46282.2916666667</v>
+      </c>
+      <c r="B1078" t="n">
+        <v>18801</v>
+      </c>
+      <c r="C1078" t="n">
+        <v>11.6400003433228</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -24984,22 +24984,22 @@
     </row>
     <row r="1071">
       <c r="A1071" s="1" t="n">
-        <v>46273.2916666667</v>
+        <v>46272.2916666667</v>
       </c>
       <c r="B1071" t="n">
-        <v>24631</v>
+        <v>6122</v>
       </c>
       <c r="C1071" t="n">
-        <v>11.3599996566772</v>
+        <v>11.1999998092651</v>
       </c>
       <c r="D1071" t="n">
-        <v>11.0200004577637</v>
+        <v>11.039999961853</v>
       </c>
       <c r="E1071" t="n">
-        <v>11.2200002670288</v>
+        <v>11.1400003433228</v>
       </c>
       <c r="F1071" t="n">
-        <v>11.3400001525879</v>
+        <v>11.1199998855591</v>
       </c>
       <c r="G1071" t="s">
         <v>7</v>
@@ -25007,22 +25007,22 @@
     </row>
     <row r="1072">
       <c r="A1072" s="1" t="n">
-        <v>46274.2916666667</v>
+        <v>46273.2916666667</v>
       </c>
       <c r="B1072" t="n">
-        <v>13687</v>
+        <v>24631</v>
       </c>
       <c r="C1072" t="n">
-        <v>11.3800001144409</v>
+        <v>11.3599996566772</v>
       </c>
       <c r="D1072" t="n">
-        <v>11.1599998474121</v>
+        <v>11.0200004577637</v>
       </c>
       <c r="E1072" t="n">
-        <v>11.3599996566772</v>
+        <v>11.2200002670288</v>
       </c>
       <c r="F1072" t="n">
-        <v>11.2799997329712</v>
+        <v>11.3400001525879</v>
       </c>
       <c r="G1072" t="s">
         <v>7</v>
@@ -25030,22 +25030,22 @@
     </row>
     <row r="1073">
       <c r="A1073" s="1" t="n">
-        <v>46275.2916666667</v>
+        <v>46274.2916666667</v>
       </c>
       <c r="B1073" t="n">
-        <v>17909</v>
+        <v>13687</v>
       </c>
       <c r="C1073" t="n">
         <v>11.3800001144409</v>
       </c>
       <c r="D1073" t="n">
-        <v>11.1199998855591</v>
+        <v>11.1599998474121</v>
       </c>
       <c r="E1073" t="n">
+        <v>11.3599996566772</v>
+      </c>
+      <c r="F1073" t="n">
         <v>11.2799997329712</v>
-      </c>
-      <c r="F1073" t="n">
-        <v>11.2200002670288</v>
       </c>
       <c r="G1073" t="s">
         <v>7</v>
@@ -25053,22 +25053,22 @@
     </row>
     <row r="1074">
       <c r="A1074" s="1" t="n">
-        <v>46276.2916666667</v>
+        <v>46275.2916666667</v>
       </c>
       <c r="B1074" t="n">
-        <v>11838</v>
+        <v>17909</v>
       </c>
       <c r="C1074" t="n">
-        <v>11.3000001907349</v>
+        <v>11.3800001144409</v>
       </c>
       <c r="D1074" t="n">
-        <v>10.9799995422363</v>
+        <v>11.1199998855591</v>
       </c>
       <c r="E1074" t="n">
-        <v>11.3000001907349</v>
+        <v>11.2799997329712</v>
       </c>
       <c r="F1074" t="n">
-        <v>11.1999998092651</v>
+        <v>11.2200002670288</v>
       </c>
       <c r="G1074" t="s">
         <v>7</v>
@@ -25076,22 +25076,22 @@
     </row>
     <row r="1075">
       <c r="A1075" s="1" t="n">
-        <v>46279.2916666667</v>
+        <v>46276.2916666667</v>
       </c>
       <c r="B1075" t="n">
-        <v>9345</v>
+        <v>11838</v>
       </c>
       <c r="C1075" t="n">
-        <v>11.2200002670288</v>
+        <v>11.3000001907349</v>
       </c>
       <c r="D1075" t="n">
         <v>10.9799995422363</v>
       </c>
       <c r="E1075" t="n">
-        <v>11.1800003051758</v>
+        <v>11.3000001907349</v>
       </c>
       <c r="F1075" t="n">
-        <v>11.1400003433228</v>
+        <v>11.1999998092651</v>
       </c>
       <c r="G1075" t="s">
         <v>7</v>
@@ -25099,22 +25099,22 @@
     </row>
     <row r="1076">
       <c r="A1076" s="1" t="n">
-        <v>46280.2916666667</v>
+        <v>46279.2916666667</v>
       </c>
       <c r="B1076" t="n">
-        <v>9676</v>
+        <v>9345</v>
       </c>
       <c r="C1076" t="n">
+        <v>11.2200002670288</v>
+      </c>
+      <c r="D1076" t="n">
+        <v>10.9799995422363</v>
+      </c>
+      <c r="E1076" t="n">
         <v>11.1800003051758</v>
       </c>
-      <c r="D1076" t="n">
-        <v>10.960000038147</v>
-      </c>
-      <c r="E1076" t="n">
+      <c r="F1076" t="n">
         <v>11.1400003433228</v>
-      </c>
-      <c r="F1076" t="n">
-        <v>11.1599998474121</v>
       </c>
       <c r="G1076" t="s">
         <v>7</v>
@@ -25122,22 +25122,22 @@
     </row>
     <row r="1077">
       <c r="A1077" s="1" t="n">
-        <v>46281.2916666667</v>
+        <v>46280.2916666667</v>
       </c>
       <c r="B1077" t="n">
-        <v>21841</v>
+        <v>9676</v>
       </c>
       <c r="C1077" t="n">
-        <v>11.6199998855591</v>
+        <v>11.1800003051758</v>
       </c>
       <c r="D1077" t="n">
-        <v>11.1000003814697</v>
+        <v>10.960000038147</v>
       </c>
       <c r="E1077" t="n">
-        <v>11.1000003814697</v>
+        <v>11.1400003433228</v>
       </c>
       <c r="F1077" t="n">
-        <v>11.5799999237061</v>
+        <v>11.1599998474121</v>
       </c>
       <c r="G1077" t="s">
         <v>7</v>
@@ -25145,24 +25145,47 @@
     </row>
     <row r="1078">
       <c r="A1078" s="1" t="n">
-        <v>46282.2916666667</v>
+        <v>46281.2916666667</v>
       </c>
       <c r="B1078" t="n">
-        <v>18801</v>
+        <v>21841</v>
       </c>
       <c r="C1078" t="n">
+        <v>11.6199998855591</v>
+      </c>
+      <c r="D1078" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="E1078" t="n">
+        <v>11.1000003814697</v>
+      </c>
+      <c r="F1078" t="n">
+        <v>11.5799999237061</v>
+      </c>
+      <c r="G1078" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1079">
+      <c r="A1079" s="1" t="n">
+        <v>46283.2916666667</v>
+      </c>
+      <c r="B1079" t="n">
+        <v>60295</v>
+      </c>
+      <c r="C1079" t="n">
+        <v>11.960000038147</v>
+      </c>
+      <c r="D1079" t="n">
         <v>11.6400003433228</v>
       </c>
-      <c r="D1078" t="n">
-        <v>11.3999996185303</v>
-      </c>
-      <c r="E1078" t="n">
-        <v>11.6000003814697</v>
-      </c>
-      <c r="F1078" t="n">
+      <c r="E1079" t="n">
         <v>11.6599998474121</v>
       </c>
-      <c r="G1078" t="s">
+      <c r="F1079" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="G1079" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28481,6 +28481,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1082">
+      <c r="A1082" s="1" t="n">
+        <v>46287.2916666667</v>
+      </c>
+      <c r="B1082" t="n">
+        <v>14605</v>
+      </c>
+      <c r="C1082" t="n">
+        <v>11.8599996566772</v>
+      </c>
+      <c r="D1082" t="n">
+        <v>11.6599998474121</v>
+      </c>
+      <c r="E1082" t="n">
+        <v>11.8599996566772</v>
+      </c>
+      <c r="F1082" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="G1082" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="H1082" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28507,6 +28507,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1083">
+      <c r="A1083" s="1" t="n">
+        <v>46288.2916666667</v>
+      </c>
+      <c r="B1083" t="n">
+        <v>24465</v>
+      </c>
+      <c r="C1083" t="n">
+        <v>11.960000038147</v>
+      </c>
+      <c r="D1083" t="n">
+        <v>11.539999961853</v>
+      </c>
+      <c r="E1083" t="n">
+        <v>11.8000001907349</v>
+      </c>
+      <c r="F1083" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="G1083" t="n">
+        <v>11.7200002670288</v>
+      </c>
+      <c r="H1083" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28533,6 +28533,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1084">
+      <c r="A1084" s="1" t="n">
+        <v>46289.2916666667</v>
+      </c>
+      <c r="B1084" t="n">
+        <v>8296</v>
+      </c>
+      <c r="C1084" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="D1084" t="n">
+        <v>11.460000038147</v>
+      </c>
+      <c r="E1084" t="n">
+        <v>11.7600002288818</v>
+      </c>
+      <c r="F1084" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="G1084" t="n">
+        <v>11.5600004196167</v>
+      </c>
+      <c r="H1084" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28559,6 +28559,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1085">
+      <c r="A1085" s="1" t="n">
+        <v>46290.2916666667</v>
+      </c>
+      <c r="B1085" t="n">
+        <v>9690</v>
+      </c>
+      <c r="C1085" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="D1085" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="E1085" t="n">
+        <v>11.6999998092651</v>
+      </c>
+      <c r="F1085" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="G1085" t="n">
+        <v>11.6000003814697</v>
+      </c>
+      <c r="H1085" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28637,6 +28637,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1088">
+      <c r="A1088" s="1" t="n">
+        <v>46295.2916666667</v>
+      </c>
+      <c r="B1088" t="n">
+        <v>36475</v>
+      </c>
+      <c r="C1088" t="n">
+        <v>11.9200000762939</v>
+      </c>
+      <c r="D1088" t="n">
+        <v>11.1999998092651</v>
+      </c>
+      <c r="E1088" t="n">
+        <v>11.4799995422363</v>
+      </c>
+      <c r="F1088" t="n">
+        <v>11.6400003433228</v>
+      </c>
+      <c r="G1088" t="n">
+        <v>11.6400003433228</v>
+      </c>
+      <c r="H1088" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25458,8 +25458,31 @@
       <c r="E1091" t="n">
         <v>11.5799999237061</v>
       </c>
-      <c r="F1091"/>
+      <c r="F1091" t="n">
+        <v>11.460000038147</v>
+      </c>
       <c r="G1091" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1092">
+      <c r="A1092" s="1" t="n">
+        <v>46301.2916666667</v>
+      </c>
+      <c r="B1092" t="n">
+        <v>17553</v>
+      </c>
+      <c r="C1092" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="D1092" t="n">
+        <v>11.2399997711182</v>
+      </c>
+      <c r="E1092" t="n">
+        <v>11.5</v>
+      </c>
+      <c r="F1092"/>
+      <c r="G1092" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25481,8 +25481,31 @@
       <c r="E1092" t="n">
         <v>11.5</v>
       </c>
-      <c r="F1092"/>
+      <c r="F1092" t="n">
+        <v>11.3400001525879</v>
+      </c>
       <c r="G1092" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1093">
+      <c r="A1093" s="1" t="n">
+        <v>46302.2916666667</v>
+      </c>
+      <c r="B1093" t="n">
+        <v>8125</v>
+      </c>
+      <c r="C1093" t="n">
+        <v>11.3599996566772</v>
+      </c>
+      <c r="D1093" t="n">
+        <v>11.0600004196167</v>
+      </c>
+      <c r="E1093" t="n">
+        <v>11.3599996566772</v>
+      </c>
+      <c r="F1093"/>
+      <c r="G1093" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25504,8 +25504,31 @@
       <c r="E1093" t="n">
         <v>11.3599996566772</v>
       </c>
-      <c r="F1093"/>
+      <c r="F1093" t="n">
+        <v>11.1400003433228</v>
+      </c>
       <c r="G1093" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1094">
+      <c r="A1094" s="1" t="n">
+        <v>46303.2916666667</v>
+      </c>
+      <c r="B1094" t="n">
+        <v>10688</v>
+      </c>
+      <c r="C1094" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="D1094" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="E1094" t="n">
+        <v>11.1199998855591</v>
+      </c>
+      <c r="F1094"/>
+      <c r="G1094" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25527,8 +25527,31 @@
       <c r="E1094" t="n">
         <v>11.1199998855591</v>
       </c>
-      <c r="F1094"/>
+      <c r="F1094" t="n">
+        <v>10.9399995803833</v>
+      </c>
       <c r="G1094" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="1095">
+      <c r="A1095" s="1" t="n">
+        <v>46304.2916666667</v>
+      </c>
+      <c r="B1095" t="n">
+        <v>18646</v>
+      </c>
+      <c r="C1095" t="n">
+        <v>11.3999996185303</v>
+      </c>
+      <c r="D1095" t="n">
+        <v>10.7600002288818</v>
+      </c>
+      <c r="E1095" t="n">
+        <v>10.960000038147</v>
+      </c>
+      <c r="F1095"/>
+      <c r="G1095" t="s">
         <v>7</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -25557,6 +25557,29 @@
         <v>7</v>
       </c>
     </row>
+    <row r="1096">
+      <c r="A1096" s="1" t="n">
+        <v>46307.2916666667</v>
+      </c>
+      <c r="B1096" t="n">
+        <v>1935</v>
+      </c>
+      <c r="C1096" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="D1096" t="n">
+        <v>11.039999961853</v>
+      </c>
+      <c r="E1096" t="n">
+        <v>11.3199996948242</v>
+      </c>
+      <c r="F1096" t="n">
+        <v>11.039999961853</v>
+      </c>
+      <c r="G1096" t="s">
+        <v>7</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28923,6 +28923,32 @@
         <v>8</v>
       </c>
     </row>
+    <row r="1099">
+      <c r="A1099" s="1" t="n">
+        <v>46310.2916666667</v>
+      </c>
+      <c r="B1099" t="n">
+        <v>9529</v>
+      </c>
+      <c r="C1099" t="n">
+        <v>11</v>
+      </c>
+      <c r="D1099" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="E1099" t="n">
+        <v>11</v>
+      </c>
+      <c r="F1099" t="n">
+        <v>10.7200002670288</v>
+      </c>
+      <c r="G1099" t="n">
+        <v>10.7200002670288</v>
+      </c>
+      <c r="H1099" t="s">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -28928,7 +28928,7 @@
         <v>46310.2916666667</v>
       </c>
       <c r="B1099" t="n">
-        <v>9529</v>
+        <v>10136</v>
       </c>
       <c r="C1099" t="n">
         <v>11</v>
@@ -28946,6 +28946,32 @@
         <v>10.7200002670288</v>
       </c>
       <c r="H1099" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="1100">
+      <c r="A1100" s="1" t="n">
+        <v>46311.2916666667</v>
+      </c>
+      <c r="B1100" t="n">
+        <v>3757</v>
+      </c>
+      <c r="C1100" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="D1100" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="E1100" t="n">
+        <v>10.8599996566772</v>
+      </c>
+      <c r="F1100" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="G1100" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="H1100" t="s">
         <v>8</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32278,6 +32278,64 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1101">
+      <c r="A1101" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1101" s="1" t="n">
+        <v>46314.2916666667</v>
+      </c>
+      <c r="C1101" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="D1101" t="n">
+        <v>10.9200000762939</v>
+      </c>
+      <c r="E1101" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="F1101" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="G1101" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="H1101" t="n">
+        <v>7564</v>
+      </c>
+      <c r="I1101" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1102">
+      <c r="A1102" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1102" s="1" t="n">
+        <v>46315.2916666667</v>
+      </c>
+      <c r="C1102" t="n">
+        <v>10.6000003814697</v>
+      </c>
+      <c r="D1102" t="n">
+        <v>10.6999998092651</v>
+      </c>
+      <c r="E1102" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="F1102" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="G1102" t="n">
+        <v>10.5799999237061</v>
+      </c>
+      <c r="H1102" t="n">
+        <v>6906</v>
+      </c>
+      <c r="I1102" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32336,6 +32336,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1103">
+      <c r="A1103" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1103" s="1" t="n">
+        <v>46316.2916666667</v>
+      </c>
+      <c r="C1103" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="D1103" t="n">
+        <v>10.7799997329712</v>
+      </c>
+      <c r="E1103" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="F1103" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="G1103" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="H1103" t="n">
+        <v>1652</v>
+      </c>
+      <c r="I1103" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32365,6 +32365,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1104">
+      <c r="A1104" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1104" s="1" t="n">
+        <v>46317.2916666667</v>
+      </c>
+      <c r="C1104" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="D1104" t="n">
+        <v>10.7399997711182</v>
+      </c>
+      <c r="E1104" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="F1104" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="G1104" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="H1104" t="n">
+        <v>5948</v>
+      </c>
+      <c r="I1104" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32394,6 +32394,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1105">
+      <c r="A1105" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1105" s="1" t="n">
+        <v>46318.2916666667</v>
+      </c>
+      <c r="C1105" t="n">
+        <v>10.460000038147</v>
+      </c>
+      <c r="D1105" t="n">
+        <v>10.460000038147</v>
+      </c>
+      <c r="E1105" t="n">
+        <v>9.68000030517578</v>
+      </c>
+      <c r="F1105" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="G1105" t="n">
+        <v>10.0799999237061</v>
+      </c>
+      <c r="H1105" t="n">
+        <v>21933</v>
+      </c>
+      <c r="I1105" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32417,9 +32417,38 @@
         <v>10.0799999237061</v>
       </c>
       <c r="H1105" t="n">
-        <v>21933</v>
+        <v>22464</v>
       </c>
       <c r="I1105" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1106">
+      <c r="A1106" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1106" s="1" t="n">
+        <v>46321.3333333333</v>
+      </c>
+      <c r="C1106" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="D1106" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="E1106" t="n">
+        <v>10.0200004577637</v>
+      </c>
+      <c r="F1106" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="G1106" t="n">
+        <v>10.1599998474121</v>
+      </c>
+      <c r="H1106" t="n">
+        <v>3745</v>
+      </c>
+      <c r="I1106" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32437,7 +32437,7 @@
         <v>10.1599998474121</v>
       </c>
       <c r="E1106" t="n">
-        <v>10.0200004577637</v>
+        <v>10</v>
       </c>
       <c r="F1106" t="n">
         <v>10.1599998474121</v>
@@ -32446,9 +32446,38 @@
         <v>10.1599998474121</v>
       </c>
       <c r="H1106" t="n">
-        <v>3745</v>
+        <v>4380</v>
       </c>
       <c r="I1106" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1107">
+      <c r="A1107" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1107" s="1" t="n">
+        <v>46322.3333333333</v>
+      </c>
+      <c r="C1107" t="n">
+        <v>10.1400003433228</v>
+      </c>
+      <c r="D1107" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="E1107" t="n">
+        <v>9.77000045776367</v>
+      </c>
+      <c r="F1107" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="G1107" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="H1107" t="n">
+        <v>42045</v>
+      </c>
+      <c r="I1107" t="s">
         <v>9</v>
       </c>
     </row>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32481,6 +32481,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1108">
+      <c r="A1108" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1108" s="1" t="n">
+        <v>46323.3333333333</v>
+      </c>
+      <c r="C1108" t="n">
+        <v>10.539999961853</v>
+      </c>
+      <c r="D1108" t="n">
+        <v>10.6199998855591</v>
+      </c>
+      <c r="E1108" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="F1108" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="G1108" t="n">
+        <v>10.4799995422363</v>
+      </c>
+      <c r="H1108" t="n">
+        <v>14448</v>
+      </c>
+      <c r="I1108" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32510,6 +32510,35 @@
         <v>9</v>
       </c>
     </row>
+    <row r="1109">
+      <c r="A1109" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1109" s="1" t="n">
+        <v>46324.3333333333</v>
+      </c>
+      <c r="C1109" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="D1109" t="n">
+        <v>10.6400003433228</v>
+      </c>
+      <c r="E1109" t="n">
+        <v>10.3800001144409</v>
+      </c>
+      <c r="F1109" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="G1109" t="n">
+        <v>10.3599996566772</v>
+      </c>
+      <c r="H1109" t="n">
+        <v>13094</v>
+      </c>
+      <c r="I1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId2"/>

--- a/data/RDF.MI.xlsx
+++ b/data/RDF.MI.xlsx
@@ -32524,7 +32524,7 @@
         <v>10.6400003433228</v>
       </c>
       <c r="E1109" t="n">
-        <v>10.3800001144409</v>
+        <v>10.3599996566772</v>
       </c>
       <c r="F1109" t="n">
         <v>10.3599996566772</v>
@@ -32536,6 +32536,35 @@
         <v>13094</v>
       </c>
       <c r="I1109" t="s">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="1110">
+      <c r="A1110" t="s">
+        <v>9</v>
+      </c>
+      <c r="B1110" s="1" t="n">
+        <v>46325.3333333333</v>
+      </c>
+      <c r="C1110" t="n">
+        <v>10.4200000762939</v>
+      </c>
+      <c r="D1110" t="n">
+        <v>10.5200004577637</v>
+      </c>
+      <c r="E1110" t="n">
+        <v>10.1999998092651</v>
+      </c>
+      <c r="F1110" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="G1110" t="n">
+        <v>10.4399995803833</v>
+      </c>
+      <c r="H1110" t="n">
+        <v>14704</v>
+      </c>
+      <c r="I1110" t="s">
         <v>9</v>
       </c>
     </row>
